--- a/DAILY SELL IN DSE.xlsx
+++ b/DAILY SELL IN DSE.xlsx
@@ -1038,11 +1038,11 @@
       </c>
       <c r="D4" s="26">
         <f>SUM(F4:AJ4)</f>
-        <v>53949000</v>
+        <v>54949000</v>
       </c>
       <c r="E4" s="24">
         <f>D4/C4</f>
-        <v>0.10967825060553095</v>
+        <v>0.11171124937484142</v>
       </c>
       <c r="F4" s="27">
         <v>4040000</v>
@@ -1069,7 +1069,7 @@
         <v>3736000</v>
       </c>
       <c r="N4" s="26">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="O4" s="26">
         <v>0</v>
@@ -1150,11 +1150,11 @@
       </c>
       <c r="D5" s="26">
         <f t="shared" ref="D5:D8" si="0">SUM(F5:AJ5)</f>
-        <v>50129000</v>
+        <v>51129000</v>
       </c>
       <c r="E5" s="24">
         <f t="shared" ref="E5:E8" si="1">D5/C5</f>
-        <v>0.14057555141088052</v>
+        <v>0.14337982740702807</v>
       </c>
       <c r="F5" s="27">
         <v>8209000</v>
@@ -1181,7 +1181,7 @@
         <v>12232000</v>
       </c>
       <c r="N5" s="26">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="O5" s="26">
         <v>0</v>
@@ -1262,11 +1262,11 @@
       </c>
       <c r="D6" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="E6" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.5729432305334294E-3</v>
       </c>
       <c r="F6" s="26">
         <v>0</v>
@@ -1287,7 +1287,7 @@
       <c r="L6" s="26"/>
       <c r="M6" s="26"/>
       <c r="N6" s="26">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="O6" s="26">
         <v>0</v>
@@ -1368,11 +1368,11 @@
       </c>
       <c r="D7" s="26">
         <f t="shared" si="0"/>
-        <v>27700000</v>
+        <v>28700000</v>
       </c>
       <c r="E7" s="24">
         <f t="shared" si="1"/>
-        <v>6.8994937182708299E-2</v>
+        <v>7.1485729138762749E-2</v>
       </c>
       <c r="F7" s="27">
         <v>2033600</v>
@@ -1399,7 +1399,7 @@
         <v>4505000</v>
       </c>
       <c r="N7" s="26">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="O7" s="26">
         <v>0</v>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="D8" s="26">
         <f t="shared" si="0"/>
-        <v>61126500</v>
+        <v>62126500</v>
       </c>
       <c r="E8" s="24">
         <f t="shared" si="1"/>
-        <v>0.17716000048578762</v>
+        <v>0.18005825247937121</v>
       </c>
       <c r="F8" s="27">
         <v>7532500</v>
@@ -1511,7 +1511,7 @@
         <v>4330000</v>
       </c>
       <c r="N8" s="26">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="O8" s="26">
         <v>0</v>

--- a/DAILY SELL IN DSE.xlsx
+++ b/DAILY SELL IN DSE.xlsx
@@ -1038,11 +1038,11 @@
       </c>
       <c r="D4" s="26">
         <f>SUM(F4:AJ4)</f>
-        <v>54949000</v>
+        <v>53949000</v>
       </c>
       <c r="E4" s="24">
         <f>D4/C4</f>
-        <v>0.11171124937484142</v>
+        <v>0.10967825060553095</v>
       </c>
       <c r="F4" s="27">
         <v>4040000</v>
@@ -1069,7 +1069,7 @@
         <v>3736000</v>
       </c>
       <c r="N4" s="26">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="O4" s="26">
         <v>0</v>
@@ -1150,11 +1150,11 @@
       </c>
       <c r="D5" s="26">
         <f t="shared" ref="D5:D8" si="0">SUM(F5:AJ5)</f>
-        <v>51129000</v>
+        <v>50129000</v>
       </c>
       <c r="E5" s="24">
         <f t="shared" ref="E5:E8" si="1">D5/C5</f>
-        <v>0.14337982740702807</v>
+        <v>0.14057555141088052</v>
       </c>
       <c r="F5" s="27">
         <v>8209000</v>
@@ -1181,7 +1181,7 @@
         <v>12232000</v>
       </c>
       <c r="N5" s="26">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="O5" s="26">
         <v>0</v>
@@ -1262,11 +1262,11 @@
       </c>
       <c r="D6" s="26">
         <f t="shared" si="0"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E6" s="24">
         <f t="shared" si="1"/>
-        <v>2.5729432305334294E-3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="26">
         <v>0</v>
@@ -1287,7 +1287,7 @@
       <c r="L6" s="26"/>
       <c r="M6" s="26"/>
       <c r="N6" s="26">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="O6" s="26">
         <v>0</v>
@@ -1368,11 +1368,11 @@
       </c>
       <c r="D7" s="26">
         <f t="shared" si="0"/>
-        <v>28700000</v>
+        <v>27700000</v>
       </c>
       <c r="E7" s="24">
         <f t="shared" si="1"/>
-        <v>7.1485729138762749E-2</v>
+        <v>6.8994937182708299E-2</v>
       </c>
       <c r="F7" s="27">
         <v>2033600</v>
@@ -1399,7 +1399,7 @@
         <v>4505000</v>
       </c>
       <c r="N7" s="26">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="O7" s="26">
         <v>0</v>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="D8" s="26">
         <f t="shared" si="0"/>
-        <v>62126500</v>
+        <v>61126500</v>
       </c>
       <c r="E8" s="24">
         <f t="shared" si="1"/>
-        <v>0.18005825247937121</v>
+        <v>0.17716000048578762</v>
       </c>
       <c r="F8" s="27">
         <v>7532500</v>
@@ -1511,7 +1511,7 @@
         <v>4330000</v>
       </c>
       <c r="N8" s="26">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="O8" s="26">
         <v>0</v>

--- a/DAILY SELL IN DSE.xlsx
+++ b/DAILY SELL IN DSE.xlsx
@@ -1038,11 +1038,11 @@
       </c>
       <c r="D4" s="26">
         <f>SUM(F4:AJ4)</f>
-        <v>53949000</v>
+        <v>67924000</v>
       </c>
       <c r="E4" s="24">
         <f>D4/C4</f>
-        <v>0.10967825060553095</v>
+        <v>0.13808940840664488</v>
       </c>
       <c r="F4" s="27">
         <v>4040000</v>
@@ -1069,7 +1069,7 @@
         <v>3736000</v>
       </c>
       <c r="N4" s="26">
-        <v>0</v>
+        <v>13975000</v>
       </c>
       <c r="O4" s="26">
         <v>0</v>
@@ -1150,11 +1150,11 @@
       </c>
       <c r="D5" s="26">
         <f t="shared" ref="D5:D8" si="0">SUM(F5:AJ5)</f>
-        <v>50129000</v>
+        <v>57944000</v>
       </c>
       <c r="E5" s="24">
         <f t="shared" ref="E5:E8" si="1">D5/C5</f>
-        <v>0.14057555141088052</v>
+        <v>0.16249096832077362</v>
       </c>
       <c r="F5" s="27">
         <v>8209000</v>
@@ -1181,7 +1181,7 @@
         <v>12232000</v>
       </c>
       <c r="N5" s="26">
-        <v>0</v>
+        <v>7815000</v>
       </c>
       <c r="O5" s="26">
         <v>0</v>
@@ -1368,11 +1368,11 @@
       </c>
       <c r="D7" s="26">
         <f t="shared" si="0"/>
-        <v>27700000</v>
+        <v>32190000</v>
       </c>
       <c r="E7" s="24">
         <f t="shared" si="1"/>
-        <v>6.8994937182708299E-2</v>
+        <v>8.0178593065392781E-2</v>
       </c>
       <c r="F7" s="27">
         <v>2033600</v>
@@ -1399,7 +1399,7 @@
         <v>4505000</v>
       </c>
       <c r="N7" s="26">
-        <v>0</v>
+        <v>4490000</v>
       </c>
       <c r="O7" s="26">
         <v>0</v>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="D8" s="26">
         <f t="shared" si="0"/>
-        <v>61126500</v>
+        <v>66455300</v>
       </c>
       <c r="E8" s="24">
         <f t="shared" si="1"/>
-        <v>0.17716000048578762</v>
+        <v>0.19260420570919587</v>
       </c>
       <c r="F8" s="27">
         <v>7532500</v>
@@ -1511,7 +1511,7 @@
         <v>4330000</v>
       </c>
       <c r="N8" s="26">
-        <v>0</v>
+        <v>5328800</v>
       </c>
       <c r="O8" s="26">
         <v>0</v>
@@ -1714,11 +1714,11 @@
       </c>
       <c r="D11" s="26">
         <f>SUM(F11:AJ11)</f>
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E11" s="24">
         <f>D11/C11</f>
-        <v>0.33205597817413585</v>
+        <v>0</v>
       </c>
       <c r="F11" s="26">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="26">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J11" s="26">
         <v>0</v>
       </c>
       <c r="K11" s="26">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L11" s="26">
         <v>0</v>
@@ -1826,11 +1826,11 @@
       </c>
       <c r="D12" s="26">
         <f t="shared" ref="D12:D15" si="2">SUM(F12:AJ12)</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E12" s="24">
         <f t="shared" ref="E12:E15" si="3">D12/C12</f>
-        <v>9.1710776660165166E-2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="26">
         <v>0</v>
@@ -1839,13 +1839,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="26">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I12" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="26">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K12" s="26">
         <v>0</v>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="D13" s="26">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="24">
         <f t="shared" si="3"/>
-        <v>2.1998859936526193E-3</v>
+        <v>0</v>
       </c>
       <c r="F13" s="26">
         <v>0</v>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="26">
         <v>0</v>
@@ -2162,11 +2162,11 @@
       </c>
       <c r="D15" s="26">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="24">
         <f t="shared" si="3"/>
-        <v>4.9442825131843348E-3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="26">
         <v>0</v>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" s="26">
         <v>0</v>

--- a/DAILY SELL IN DSE.xlsx
+++ b/DAILY SELL IN DSE.xlsx
@@ -315,8 +315,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -448,7 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -471,21 +471,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="169" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>130352000</v>
+        <v>144916500</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.20964978285008767</v>
+        <v>0.23307438901125208</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-491408720.32094395</v>
+        <v>-476844220.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-27300484.462274663</v>
+        <v>-26491345.573385775</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>83255000</v>
+        <v>125575000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.14476183053911834</v>
+        <v>0.21834684847696578</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-491862071.19165206</v>
+        <v>-449542071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-27325670.621758446</v>
+        <v>-24974559.510647338</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>44927200</v>
+        <v>54900400</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.18581494906417514</v>
+        <v>0.22706322739015208</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-196857436.953421</v>
+        <v>-186884236.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-10936524.275190055</v>
+        <v>-10382457.608523389</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>89183000</v>
+        <v>104129000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.19733373377579566</v>
+        <v>0.230404498215353</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-362756961.27051902</v>
+        <v>-347810961.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-20153164.515028834</v>
+        <v>-19322831.181695502</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -999,19 +999,19 @@
         <v>744.32125870725895</v>
       </c>
       <c r="D11" s="10">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.43798292227498448</v>
+        <v>0.62204323010220186</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-418.32125870725895</v>
+        <v>-281.32125870725895</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-23.240069928181054</v>
+        <v>-15.628958817069941</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>151</v>
+        <v>235</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.37941500310300796</v>
+        <v>0.59048030284242969</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-246.981099231874</v>
+        <v>-162.981099231874</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-13.721172179548555</v>
+        <v>-9.0545055128818888</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.31100508642549091</v>
+        <v>0.40338283486870607</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-223.753531078332</v>
+        <v>-193.753531078332</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-12.430751726574</v>
+        <v>-10.764085059907334</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.25591013484050729</v>
+        <v>0.29354397819940542</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-296.57741493344997</v>
+        <v>-281.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-16.476523051858333</v>
+        <v>-15.643189718524999</v>
       </c>
     </row>
     <row r="16" spans="1:7">
